--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post FET_HRM-2031-0132/Panel 02/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post FET_HRM-2031-0132/Panel 02/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,595 +413,736 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="C1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Measured by operator 7 on tool HRM-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Max Stepheight</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Min Stepheight</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Mean Stepheight</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Trace 1</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>16.50235</v>
-      </c>
-      <c r="D2" t="n">
-        <v>15.87895</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16.55322</v>
-      </c>
-      <c r="F2" t="n">
-        <v>22.04595</v>
-      </c>
-      <c r="G2" t="n">
-        <v>21.77796</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.04631</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.66857</v>
+        <v>16.8628</v>
       </c>
       <c r="D3" t="n">
-        <v>16.30195</v>
+        <v>16.66146</v>
       </c>
       <c r="E3" t="n">
-        <v>16.2182</v>
+        <v>16.72421</v>
       </c>
       <c r="F3" t="n">
-        <v>21.6443</v>
+        <v>42.54876</v>
       </c>
       <c r="G3" t="n">
-        <v>21.47562</v>
+        <v>0.051</v>
       </c>
       <c r="H3" t="n">
-        <v>34.20163</v>
+        <v>1.83353</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.42057</v>
+        <v>17.00428</v>
       </c>
       <c r="D4" t="n">
-        <v>16.01216</v>
+        <v>16.2771</v>
       </c>
       <c r="E4" t="n">
-        <v>16.41757</v>
+        <v>16.82553</v>
       </c>
       <c r="F4" t="n">
-        <v>21.74955</v>
+        <v>41.92344</v>
       </c>
       <c r="G4" t="n">
-        <v>22.46716</v>
+        <v>0.04931</v>
       </c>
       <c r="H4" t="n">
-        <v>34.03218</v>
+        <v>1.80445</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.63919</v>
+        <v>17.04787</v>
       </c>
       <c r="D5" t="n">
-        <v>15.97173</v>
+        <v>16.45211</v>
       </c>
       <c r="E5" t="n">
-        <v>16.30156</v>
+        <v>16.63524</v>
       </c>
       <c r="F5" t="n">
-        <v>21.85693</v>
+        <v>42.22632</v>
       </c>
       <c r="G5" t="n">
-        <v>21.74897</v>
+        <v>0.05058</v>
       </c>
       <c r="H5" t="n">
-        <v>34.25811</v>
+        <v>1.79182</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.86372</v>
+        <v>16.94298</v>
       </c>
       <c r="D6" t="n">
-        <v>15.42531</v>
+        <v>16.56082</v>
       </c>
       <c r="E6" t="n">
-        <v>16.29398</v>
+        <v>16.83924</v>
       </c>
       <c r="F6" t="n">
-        <v>21.58449</v>
+        <v>42.6432</v>
       </c>
       <c r="G6" t="n">
-        <v>22.36496</v>
+        <v>0.05055</v>
       </c>
       <c r="H6" t="n">
-        <v>34.29811</v>
+        <v>1.83479</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.5046</v>
+        <v>16.80492</v>
       </c>
       <c r="D7" t="n">
-        <v>15.81701</v>
+        <v>16.27446</v>
       </c>
       <c r="E7" t="n">
-        <v>16.35236</v>
+        <v>16.45079</v>
       </c>
       <c r="F7" t="n">
-        <v>21.76423</v>
+        <v>42.69371</v>
       </c>
       <c r="G7" t="n">
-        <v>22.1468</v>
+        <v>0.05023</v>
       </c>
       <c r="H7" t="n">
-        <v>33.16187</v>
+        <v>1.83349</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.65512</v>
+        <v>16.93367</v>
       </c>
       <c r="D8" t="n">
-        <v>16.04337</v>
+        <v>16.3069</v>
       </c>
       <c r="E8" t="n">
-        <v>16.33735</v>
+        <v>16.68215</v>
       </c>
       <c r="F8" t="n">
-        <v>21.73867</v>
+        <v>42.02251</v>
       </c>
       <c r="G8" t="n">
-        <v>21.92145</v>
+        <v>0.05081</v>
       </c>
       <c r="H8" t="n">
-        <v>33.77171</v>
+        <v>1.78478</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.00355</v>
+        <v>17.0846</v>
       </c>
       <c r="D9" t="n">
-        <v>16.00563</v>
+        <v>16.47217</v>
       </c>
       <c r="E9" t="n">
-        <v>16.30533</v>
+        <v>17.00655</v>
       </c>
       <c r="F9" t="n">
-        <v>21.50095</v>
+        <v>42.77736</v>
       </c>
       <c r="G9" t="n">
-        <v>21.57926</v>
+        <v>0.05129</v>
       </c>
       <c r="H9" t="n">
-        <v>34.78234</v>
+        <v>1.81074</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>16.83465</v>
+      </c>
+      <c r="D10" t="n">
+        <v>16.54213</v>
+      </c>
+      <c r="E10" t="n">
+        <v>16.64228</v>
+      </c>
+      <c r="F10" t="n">
+        <v>42.76397</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05025</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.83276</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>16.36476</v>
-      </c>
-      <c r="D10" t="n">
-        <v>16.29553</v>
-      </c>
-      <c r="E10" t="n">
-        <v>16.90274</v>
-      </c>
-      <c r="F10" t="n">
-        <v>22.10236</v>
-      </c>
-      <c r="G10" t="n">
-        <v>21.6076</v>
-      </c>
-      <c r="H10" t="n">
-        <v>34.24072</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
+      <c r="C11" t="n">
+        <v>16.81287</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.64089</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.72274</v>
+      </c>
+      <c r="F11" t="n">
+        <v>42.33751</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.05151</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.81962</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>roughness</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.73449</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.08151</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.61142</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.94381</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.11014</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.00753</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.09254</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.12581</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.74157</v>
+        <v>0.60462</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07990999999999999</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.60794</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.96868</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.10858</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.00756</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.09365</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.12661</v>
+        <v>1.11713</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.7408</v>
+        <v>0.61004</v>
       </c>
       <c r="D14" t="n">
-        <v>0.08144999999999999</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.60858</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.96366</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.10583</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.00748</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.09376</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.12723</v>
+        <v>1.1155</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.7638</v>
+        <v>0.60214</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08116</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.59211</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.96823</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.11133</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.00745</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.09182999999999999</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.12634</v>
+        <v>1.11581</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.75076</v>
+        <v>0.61258</v>
       </c>
       <c r="D16" t="n">
-        <v>0.08032</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.60438</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.95731</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.10862</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.00754</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.09357</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.12877</v>
+        <v>1.08499</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.75845</v>
+        <v>0.61041</v>
       </c>
       <c r="D17" t="n">
-        <v>0.08173999999999999</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.61329</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.96393</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.11037</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.00771</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.09271</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.12805</v>
+        <v>1.12249</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.75654</v>
+        <v>0.6137899999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>0.07939</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.61738</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.94369</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.10949</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.00761</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.09247</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.12371</v>
+        <v>1.10828</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.75488</v>
+        <v>0.60012</v>
       </c>
       <c r="D19" t="n">
-        <v>0.08069999999999999</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.59903</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.96592</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.11098</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.00749</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.09371</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.12529</v>
+        <v>1.09583</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.60621</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.09132</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>0.76594</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.08169</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.62291</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.95658</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.11005</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.00772</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.09499</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.12694</v>
+      <c r="C21" t="n">
+        <v>0.6180600000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.11064</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.76257</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.08119999999999999</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.61891</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.95897</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.10976</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.09248000000000001</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.1281</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.76874</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0819</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.60425</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.97054</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.1107</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.00757</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.09172</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.12702</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.73477</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.08119999999999999</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.61132</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.95603</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.11015</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.09329</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.12781</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.74844</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.08128000000000001</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.59799</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.96567</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.09336999999999999</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.12417</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.74005</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.08132</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.61432</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.9613</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.11091</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.09163</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.1254</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7472</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.08017000000000001</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.6143999999999999</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.94023</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.11122</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.09248000000000001</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.12557</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.74263</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.08075</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.61069</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.96743</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.10968</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.0927</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.12799</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.74544</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.08097</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.6214</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.97051</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.10941</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.00757</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.09223000000000001</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.12523</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.74092</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.08272</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.60848</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.96043</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.10979</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.00751</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.09379</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.12934</v>
       </c>
     </row>
   </sheetData>
